--- a/data/trans_camb/P16A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,66</t>
+          <t>-1,17; 2,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,27</t>
+          <t>-2,11; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,47</t>
+          <t>-0,21; 3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,28</t>
+          <t>1,48; 6,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,79</t>
+          <t>2,18; 6,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,88</t>
+          <t>1,86; 5,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,91</t>
+          <t>0,85; 3,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,53</t>
+          <t>0,47; 3,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,13</t>
+          <t>1,46; 4,14</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 130,29</t>
+          <t>-33,49; 116,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,55; 62,32</t>
+          <t>-56,67; 67,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 164,37</t>
+          <t>-7,24; 165,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,08; 268,34</t>
+          <t>26,08; 253,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,21; 288,82</t>
+          <t>46,56; 299,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,66; 258,21</t>
+          <t>37,0; 240,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 160,33</t>
+          <t>21,08; 150,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 145,87</t>
+          <t>11,53; 147,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,77; 176,41</t>
+          <t>37,51; 166,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,89</t>
+          <t>-0,98; 2,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,98</t>
+          <t>-0,87; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,77</t>
+          <t>-1,66; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,89</t>
+          <t>0,14; 4,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,31</t>
+          <t>-1,28; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,82</t>
+          <t>2,19; 6,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,8</t>
+          <t>0,04; 2,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,12</t>
+          <t>-0,7; 2,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,39</t>
+          <t>-0,59; 3,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 102,07</t>
+          <t>-31,91; 109,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 106,25</t>
+          <t>-27,83; 113,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 93,78</t>
+          <t>-51,16; 87,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 108,71</t>
+          <t>0,66; 102,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 76,04</t>
+          <t>-20,04; 69,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 148,36</t>
+          <t>30,93; 151,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 83,1</t>
+          <t>0,81; 80,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 61,8</t>
+          <t>-15,22; 58,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 92,07</t>
+          <t>-9,95; 93,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,3</t>
+          <t>-0,45; 3,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,82</t>
+          <t>0,3; 3,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,87</t>
+          <t>1,16; 5,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,84</t>
+          <t>-3,41; 1,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,26</t>
+          <t>-1,81; 3,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,81</t>
+          <t>-4,79; 1,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,88</t>
+          <t>-1,44; 1,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,07</t>
+          <t>-0,31; 3,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,86</t>
+          <t>-1,05; 2,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 249,6</t>
+          <t>-21,8; 266,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 288,62</t>
+          <t>3,26; 308,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,12; 372,17</t>
+          <t>32,37; 471,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,37; 32,58</t>
+          <t>-41,92; 33,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 56,62</t>
+          <t>-23,22; 66,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 29,52</t>
+          <t>-58,65; 31,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 54,44</t>
+          <t>-27,89; 51,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 85,94</t>
+          <t>-6,25; 81,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 78,32</t>
+          <t>-19,9; 74,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,73</t>
+          <t>-0,8; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,11</t>
+          <t>-0,21; 3,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,98</t>
+          <t>0,49; 3,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,92</t>
+          <t>-0,31; 3,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,82</t>
+          <t>1,04; 5,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,18</t>
+          <t>0,37; 5,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,81</t>
+          <t>-0,07; 2,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,06</t>
+          <t>0,95; 3,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,92</t>
+          <t>1,11; 4,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 128,28</t>
+          <t>-23,6; 131,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 136,96</t>
+          <t>-8,15; 159,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 185,76</t>
+          <t>12,58; 181,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 90,82</t>
+          <t>-5,34; 85,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,57; 133,74</t>
+          <t>15,44; 131,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 117,12</t>
+          <t>5,69; 115,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 79,74</t>
+          <t>-2,08; 75,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,26; 117,29</t>
+          <t>20,45; 110,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,39; 111,54</t>
+          <t>22,92; 109,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,67</t>
+          <t>-0,03; 1,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,8</t>
+          <t>0,11; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,53</t>
+          <t>0,49; 2,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,86</t>
+          <t>0,56; 2,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,55</t>
+          <t>1,14; 3,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,79</t>
+          <t>1,1; 3,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,07</t>
+          <t>0,58; 2,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,36</t>
+          <t>0,91; 2,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,94</t>
+          <t>1,11; 2,92</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 77,42</t>
+          <t>-2,94; 75,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,03; 81,07</t>
+          <t>2,09; 82,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,21; 112,3</t>
+          <t>18,27; 108,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,35; 58,08</t>
+          <t>10,3; 62,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,88; 74,19</t>
+          <t>20,46; 74,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,05; 79,45</t>
+          <t>18,63; 81,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,69; 56,02</t>
+          <t>13,68; 57,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,77; 65,12</t>
+          <t>21,25; 67,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,13; 81,43</t>
+          <t>27,45; 80,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,74</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,55</t>
+          <t>-1,32; 2,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,31</t>
+          <t>-2,23; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,55</t>
+          <t>-0,49; 3,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,08</t>
+          <t>1,34; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,99</t>
+          <t>1,91; 6,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,64</t>
+          <t>1,86; 5,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,79</t>
+          <t>0,71; 3,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,6</t>
+          <t>0,52; 3,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,14</t>
+          <t>1,46; 4,15</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>119,27%</t>
+          <t>116,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 116,26</t>
+          <t>-37,85; 119,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 67,07</t>
+          <t>-60,08; 64,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 165,77</t>
+          <t>-15,55; 166,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,08; 253,91</t>
+          <t>29,26; 251,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,56; 299,57</t>
+          <t>40,59; 294,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 240,74</t>
+          <t>41,29; 250,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,08; 150,12</t>
+          <t>19,75; 155,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 147,42</t>
+          <t>10,69; 150,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,51; 166,63</t>
+          <t>37,95; 173,94</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,02</t>
+          <t>-1,05; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,1</t>
+          <t>-0,94; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,74</t>
+          <t>-0,85; 2,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,66</t>
+          <t>0,06; 4,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,17</t>
+          <t>-1,21; 3,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,74</t>
+          <t>2,4; 6,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,83</t>
+          <t>-0,07; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,02</t>
+          <t>-0,66; 2,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,33</t>
+          <t>1,14; 3,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 109,07</t>
+          <t>-34,3; 93,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 113,35</t>
+          <t>-32,57; 108,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 87,43</t>
+          <t>-25,65; 113,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 102,65</t>
+          <t>0,86; 98,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 69,79</t>
+          <t>-17,75; 75,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,93; 151,86</t>
+          <t>36,12; 146,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 80,94</t>
+          <t>-1,64; 82,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 58,8</t>
+          <t>-14,49; 61,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 93,44</t>
+          <t>21,31; 110,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,36</t>
+          <t>-0,47; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,82</t>
+          <t>0,17; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,25</t>
+          <t>1,16; 4,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,71</t>
+          <t>-3,73; 1,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,44</t>
+          <t>-2,33; 3,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,92</t>
+          <t>-1,89; 3,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,85</t>
+          <t>-1,38; 1,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,04</t>
+          <t>-0,28; 2,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,8</t>
+          <t>0,37; 3,29</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156,09%</t>
+          <t>151,9%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,34%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 266,94</t>
+          <t>-25,33; 276,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 308,88</t>
+          <t>2,89; 289,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,37; 471,0</t>
+          <t>31,73; 390,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 33,28</t>
+          <t>-43,41; 29,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 66,41</t>
+          <t>-28,99; 53,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 31,73</t>
+          <t>-22,66; 57,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 51,06</t>
+          <t>-27,69; 50,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 81,79</t>
+          <t>-6,15; 78,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 74,53</t>
+          <t>6,5; 93,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,69</t>
+          <t>-0,98; 2,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,26</t>
+          <t>-0,1; 3,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,82</t>
+          <t>0,47; 3,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,84</t>
+          <t>-0,46; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,69</t>
+          <t>0,97; 5,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,17</t>
+          <t>0,88; 4,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,74</t>
+          <t>0,02; 2,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,8</t>
+          <t>0,97; 3,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,01</t>
+          <t>1,27; 3,8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 131,31</t>
+          <t>-27,65; 125,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 159,49</t>
+          <t>-5,85; 166,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,58; 181,97</t>
+          <t>10,45; 172,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 85,96</t>
+          <t>-8,36; 82,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,44; 131,14</t>
+          <t>13,26; 122,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 115,71</t>
+          <t>13,24; 111,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 75,44</t>
+          <t>0,42; 77,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,45; 110,74</t>
+          <t>19,55; 107,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,92; 109,0</t>
+          <t>25,49; 110,63</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,64</t>
+          <t>-0,14; 1,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,79</t>
+          <t>0,12; 1,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,45</t>
+          <t>0,8; 2,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,99</t>
+          <t>0,54; 2,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,52</t>
+          <t>1,09; 3,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,89</t>
+          <t>1,94; 4,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,59; 2,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,4</t>
+          <t>0,91; 2,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,92</t>
+          <t>1,74; 3,13</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 75,01</t>
+          <t>-5,31; 72,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,09; 82,39</t>
+          <t>3,01; 81,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18,27; 108,79</t>
+          <t>25,63; 115,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,3; 62,99</t>
+          <t>8,32; 60,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,46; 74,39</t>
+          <t>17,47; 72,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,63; 81,67</t>
+          <t>32,69; 85,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,68; 57,31</t>
+          <t>12,89; 56,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,25; 67,13</t>
+          <t>20,4; 63,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>27,45; 80,19</t>
+          <t>40,09; 86,95</t>
         </is>
       </c>
     </row>
